--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>128653637</v>
       </c>
       <c r="B2" t="n">
-        <v>105899</v>
+        <v>106414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -775,6 +775,480 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128653639</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>698</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sen fältgentiana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hundsjön V om, ost Lännav., Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>699448</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6624364</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogskörväg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Lisel Hamring, Karin Hendahl, Emelie Envall, Cecilia Fransson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130110726</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>698</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sen fältgentiana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hundsjöns naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>699465</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6624376</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Väg</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På och intill skogsväg i början av Hundsjöns naturreservat</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emelie Envall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emelie Envall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128653636</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83322</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4196</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig jordtunga</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geoglossum fallax</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hundsjön V om, ost Lännav., Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>699469</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6624380</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogskörväg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Lisel Hamring, Karin Hendahl, Emelie Envall, Cecilia Fransson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128653638</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83322</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4196</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig jordtunga</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geoglossum fallax</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hundsjön V om, ost Lännav., Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>699514</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6624420</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sporer 84-98 um långa - upp till 12-septa. Parafyser ofta krökta och svällda i toppen.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogskörväg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Lisel Hamring, Karin Hendahl, Emelie Envall, Cecilia Fransson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128653637</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128653639</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130110726</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128653636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,8 +1278,20 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128653638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,52 +1043,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128653636</v>
+        <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>83322</v>
+        <v>106606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4196</v>
+        <v>698</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig jordtunga</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geoglossum fallax</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>E.J.Durand</t>
-        </is>
-      </c>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hundsjön V om, ost Lännav., Upl</t>
+          <t>Hundsjön, 500 m VNV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699469</v>
+        <v>699517</v>
       </c>
       <c r="R5" t="n">
-        <v>6624380</v>
+        <v>6624421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,12 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,68 +1139,58 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Lisel Hamring, Karin Hendahl, Emelie Envall, Cecilia Fransson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>BSIS - Floraväkteri-exkursion</t>
-        </is>
-      </c>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128653636</t>
+          <t>https://artportalen.se/Sighting/136151583</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128653638</v>
+        <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>83322</v>
+        <v>106606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4196</v>
+        <v>698</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig jordtunga</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geoglossum fallax</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>E.J.Durand</t>
-        </is>
-      </c>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hundsjön V om, ost Lännav., Upl</t>
+          <t>Hundsjön, 500 m VNV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699514</v>
+        <v>699492</v>
       </c>
       <c r="R6" t="n">
-        <v>6624420</v>
+        <v>6624399</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,17 +1217,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sporer 84-98 um långa - upp till 12-septa. Parafyser ofta krökta och svällda i toppen.</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1231,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1270,15 +1247,254 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136151584</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128653636</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83322</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4196</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig jordtunga</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Geoglossum fallax</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hundsjön V om, ost Lännav., Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>699469</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6624380</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Skogskörväg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Jan Yngve Andersson, Lisel Hamring, Karin Hendahl, Emelie Envall, Cecilia Fransson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128653636</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128653638</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83322</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4196</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig jordtunga</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Geoglossum fallax</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hundsjön V om, ost Lännav., Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>699514</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6624420</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sporer 84-98 um långa - upp till 12-septa. Parafyser ofta krökta och svällda i toppen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogskörväg</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Lisel Hamring, Karin Hendahl, Emelie Envall, Cecilia Fransson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128653638</t>
         </is>
@@ -1291,6 +1507,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106606</v>
+        <v>106607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106606</v>
+        <v>106607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106607</v>
+        <v>106608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106607</v>
+        <v>106608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106608</v>
+        <v>106614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106608</v>
+        <v>106614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106614</v>
+        <v>106615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106614</v>
+        <v>106615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106615</v>
+        <v>106626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106615</v>
+        <v>106626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106626</v>
+        <v>106639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106626</v>
+        <v>106639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106639</v>
+        <v>106640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106639</v>
+        <v>106640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106640</v>
+        <v>106653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106640</v>
+        <v>106653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106653</v>
+        <v>106654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106653</v>
+        <v>106654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
